--- a/fixtures/pkgreviewtest/inst/extdata/pkgreviewtest.xlsx
+++ b/fixtures/pkgreviewtest/inst/extdata/pkgreviewtest.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -385,6 +385,11 @@
           <t>users_count</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>owner_phone</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -415,6 +420,11 @@
       <c r="F2">
         <v>377</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>+41 79 137 11 23</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -445,6 +455,11 @@
       <c r="F3">
         <v>70</v>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>+41 79 174 22 46</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -475,6 +490,11 @@
       <c r="F4">
         <v>269</v>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>+41 79 211 33 69</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -505,6 +525,11 @@
       <c r="F5">
         <v>330</v>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>+41 79 248 44 92</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -535,6 +560,11 @@
       <c r="F6">
         <v>335</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>+41 79 285 55 15</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -565,6 +595,11 @@
       <c r="F7">
         <v>-99</v>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>+41 79 322 66 38</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -595,6 +630,11 @@
       <c r="F8">
         <v>329</v>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>+41 79 359 77 61</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -625,6 +665,11 @@
       <c r="F9">
         <v>165</v>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>+41 79 396 88 84</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -655,6 +700,11 @@
       <c r="F10">
         <v>78</v>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>+41 79 433 99 07</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -685,6 +735,11 @@
       <c r="F11">
         <v>358</v>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>+41 79 470 10 30</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -715,6 +770,11 @@
       <c r="F12">
         <v>254</v>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>+41 79 507 21 53</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -745,6 +805,11 @@
       <c r="F13">
         <v>-99</v>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>+41 79 544 32 76</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -775,6 +840,11 @@
       <c r="F14">
         <v>57</v>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>+41 79 581 43 99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -805,6 +875,11 @@
       <c r="F15">
         <v>37</v>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>+41 79 618 54 22</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -835,6 +910,11 @@
       <c r="F16">
         <v>259</v>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>+41 79 655 65 45</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -865,6 +945,11 @@
       <c r="F17">
         <v>186</v>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>+41 79 692 76 68</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -895,6 +980,11 @@
       <c r="F18">
         <v>175</v>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>+41 79 729 87 91</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -925,6 +1015,11 @@
       <c r="F19">
         <v>254</v>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>+41 79 766 98 14</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -955,6 +1050,11 @@
       <c r="F20">
         <v>-99</v>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>+41 79 803 09 37</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -985,6 +1085,11 @@
       <c r="F21">
         <v>49</v>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>+41 79 840 20 60</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1015,6 +1120,11 @@
       <c r="F22">
         <v>48</v>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>+41 79 877 31 83</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1045,6 +1155,11 @@
       <c r="F23">
         <v>132</v>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>+41 79 914 42 06</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1075,6 +1190,11 @@
       <c r="F24">
         <v>115</v>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>+41 79 951 53 29</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1105,6 +1225,11 @@
       <c r="F25">
         <v>291</v>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>+41 79 988 64 52</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1135,6 +1260,11 @@
       <c r="F26">
         <v>-99</v>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>+41 79 125 75 75</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1165,6 +1295,11 @@
       <c r="F27">
         <v>112</v>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>+41 79 162 86 98</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1195,6 +1330,11 @@
       <c r="F28">
         <v>230</v>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>+41 79 199 97 21</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1225,6 +1365,11 @@
       <c r="F29">
         <v>42</v>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>+41 79 236 08 44</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1255,6 +1400,11 @@
       <c r="F30">
         <v>303</v>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>+41 79 273 19 67</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1284,6 +1434,11 @@
       </c>
       <c r="F31">
         <v>28</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>+41 79 310 30 90</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/fixtures/pkgreviewtest/inst/extdata/pkgreviewtest.xlsx
+++ b/fixtures/pkgreviewtest/inst/extdata/pkgreviewtest.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -390,6 +390,21 @@
           <t>owner_phone</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>women_users</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -425,6 +440,15 @@
           <t>+41 79 137 11 23</t>
         </is>
       </c>
+      <c r="H2">
+        <v>150</v>
+      </c>
+      <c r="I2">
+        <v>46.27</v>
+      </c>
+      <c r="J2">
+        <v>6.31</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -460,6 +484,15 @@
           <t>+41 79 174 22 46</t>
         </is>
       </c>
+      <c r="H3">
+        <v>28</v>
+      </c>
+      <c r="I3">
+        <v>46.34</v>
+      </c>
+      <c r="J3">
+        <v>6.42</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -495,6 +528,15 @@
           <t>+41 79 211 33 69</t>
         </is>
       </c>
+      <c r="H4">
+        <v>107</v>
+      </c>
+      <c r="I4">
+        <v>46.41</v>
+      </c>
+      <c r="J4">
+        <v>6.53</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -530,6 +572,15 @@
           <t>+41 79 248 44 92</t>
         </is>
       </c>
+      <c r="H5">
+        <v>355</v>
+      </c>
+      <c r="I5">
+        <v>46.48</v>
+      </c>
+      <c r="J5">
+        <v>6.64</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -565,6 +616,15 @@
           <t>+41 79 285 55 15</t>
         </is>
       </c>
+      <c r="H6">
+        <v>134</v>
+      </c>
+      <c r="I6">
+        <v>46.55</v>
+      </c>
+      <c r="J6">
+        <v>6.75</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -600,6 +660,15 @@
           <t>+41 79 322 66 38</t>
         </is>
       </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>46.62</v>
+      </c>
+      <c r="J7">
+        <v>6.86</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -635,6 +704,15 @@
           <t>+41 79 359 77 61</t>
         </is>
       </c>
+      <c r="H8">
+        <v>131</v>
+      </c>
+      <c r="I8">
+        <v>46.69</v>
+      </c>
+      <c r="J8">
+        <v>6.97</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -670,6 +748,15 @@
           <t>+41 79 396 88 84</t>
         </is>
       </c>
+      <c r="H9">
+        <v>66</v>
+      </c>
+      <c r="I9">
+        <v>46.76</v>
+      </c>
+      <c r="J9">
+        <v>7.08</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -705,6 +792,15 @@
           <t>+41 79 433 99 07</t>
         </is>
       </c>
+      <c r="H10">
+        <v>31</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -740,6 +836,15 @@
           <t>+41 79 470 10 30</t>
         </is>
       </c>
+      <c r="H11">
+        <v>143</v>
+      </c>
+      <c r="I11">
+        <v>46.9</v>
+      </c>
+      <c r="J11">
+        <v>7.3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -775,6 +880,15 @@
           <t>+41 79 507 21 53</t>
         </is>
       </c>
+      <c r="H12">
+        <v>101</v>
+      </c>
+      <c r="I12">
+        <v>46.97</v>
+      </c>
+      <c r="J12">
+        <v>7.41</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -810,6 +924,15 @@
           <t>+41 79 544 32 76</t>
         </is>
       </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>47.04</v>
+      </c>
+      <c r="J13">
+        <v>7.52</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -845,6 +968,15 @@
           <t>+41 79 581 43 99</t>
         </is>
       </c>
+      <c r="H14">
+        <v>22</v>
+      </c>
+      <c r="I14">
+        <v>47.11</v>
+      </c>
+      <c r="J14">
+        <v>7.63</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -880,6 +1012,15 @@
           <t>+41 79 618 54 22</t>
         </is>
       </c>
+      <c r="H15">
+        <v>14</v>
+      </c>
+      <c r="I15">
+        <v>47.18</v>
+      </c>
+      <c r="J15">
+        <v>7.74</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -915,6 +1056,15 @@
           <t>+41 79 655 65 45</t>
         </is>
       </c>
+      <c r="H16">
+        <v>103</v>
+      </c>
+      <c r="I16">
+        <v>47.25</v>
+      </c>
+      <c r="J16">
+        <v>7.85</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -950,6 +1100,15 @@
           <t>+41 79 692 76 68</t>
         </is>
       </c>
+      <c r="H17">
+        <v>74</v>
+      </c>
+      <c r="I17">
+        <v>47.32</v>
+      </c>
+      <c r="J17">
+        <v>7.96</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -985,6 +1144,15 @@
           <t>+41 79 729 87 91</t>
         </is>
       </c>
+      <c r="H18">
+        <v>70</v>
+      </c>
+      <c r="I18">
+        <v>47.39</v>
+      </c>
+      <c r="J18">
+        <v>8.07</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1020,6 +1188,15 @@
           <t>+41 79 766 98 14</t>
         </is>
       </c>
+      <c r="H19">
+        <v>101</v>
+      </c>
+      <c r="I19">
+        <v>47.46</v>
+      </c>
+      <c r="J19">
+        <v>8.18</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1055,6 +1232,15 @@
           <t>+41 79 803 09 37</t>
         </is>
       </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>47.53</v>
+      </c>
+      <c r="J20">
+        <v>8.289999999999999</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1090,6 +1276,15 @@
           <t>+41 79 840 20 60</t>
         </is>
       </c>
+      <c r="H21">
+        <v>19</v>
+      </c>
+      <c r="I21">
+        <v>46.2</v>
+      </c>
+      <c r="J21">
+        <v>8.4</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1125,6 +1320,15 @@
           <t>+41 79 877 31 83</t>
         </is>
       </c>
+      <c r="H22">
+        <v>19</v>
+      </c>
+      <c r="I22">
+        <v>46.27</v>
+      </c>
+      <c r="J22">
+        <v>181.5</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1160,6 +1364,15 @@
           <t>+41 79 914 42 06</t>
         </is>
       </c>
+      <c r="H23">
+        <v>157</v>
+      </c>
+      <c r="I23">
+        <v>46.34</v>
+      </c>
+      <c r="J23">
+        <v>8.619999999999999</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1195,6 +1408,15 @@
           <t>+41 79 951 53 29</t>
         </is>
       </c>
+      <c r="H24">
+        <v>46</v>
+      </c>
+      <c r="I24">
+        <v>46.41</v>
+      </c>
+      <c r="J24">
+        <v>8.73</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1230,6 +1452,15 @@
           <t>+41 79 988 64 52</t>
         </is>
       </c>
+      <c r="H25">
+        <v>116</v>
+      </c>
+      <c r="I25">
+        <v>46.48</v>
+      </c>
+      <c r="J25">
+        <v>8.84</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1265,6 +1496,15 @@
           <t>+41 79 125 75 75</t>
         </is>
       </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>46.55</v>
+      </c>
+      <c r="J26">
+        <v>8.949999999999999</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1300,6 +1540,15 @@
           <t>+41 79 162 86 98</t>
         </is>
       </c>
+      <c r="H27">
+        <v>44</v>
+      </c>
+      <c r="I27">
+        <v>46.62</v>
+      </c>
+      <c r="J27">
+        <v>9.06</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1335,6 +1584,15 @@
           <t>+41 79 199 97 21</t>
         </is>
       </c>
+      <c r="H28">
+        <v>92</v>
+      </c>
+      <c r="I28">
+        <v>46.69</v>
+      </c>
+      <c r="J28">
+        <v>9.17</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1370,6 +1628,15 @@
           <t>+41 79 236 08 44</t>
         </is>
       </c>
+      <c r="H29">
+        <v>16</v>
+      </c>
+      <c r="I29">
+        <v>46.76</v>
+      </c>
+      <c r="J29">
+        <v>9.279999999999999</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1405,6 +1672,15 @@
           <t>+41 79 273 19 67</t>
         </is>
       </c>
+      <c r="H30">
+        <v>121</v>
+      </c>
+      <c r="I30">
+        <v>46.83</v>
+      </c>
+      <c r="J30">
+        <v>9.390000000000001</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1439,6 +1715,15 @@
         <is>
           <t>+41 79 310 30 90</t>
         </is>
+      </c>
+      <c r="H31">
+        <v>11</v>
+      </c>
+      <c r="I31">
+        <v>46.9</v>
+      </c>
+      <c r="J31">
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>
